--- a/data/input/remove_items/remove.xlsx
+++ b/data/input/remove_items/remove.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">كود</t>
   </si>
@@ -53,6 +53,21 @@
   </si>
   <si>
     <t xml:space="preserve">mnr skin bonetab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTI-COLLA ADVANCE 10 SACHET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTODINE 20 MG 3 AMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVIL 6 AMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BETADINE SHAMPOO 120ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIO GAINERS CHOCOLATE 330 GM*10 SACHETS</t>
   </si>
 </sst>
 </file>
@@ -90,6 +105,7 @@
       <color theme="1"/>
       <name val="Noto Sans Devanagari"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,12 +150,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -149,6 +169,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -171,34 +195,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -343,58 +367,96 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>47273</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1"/>
+      <c r="B7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>74696</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>73396</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>17028</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
+        <v>10512</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
